--- a/data/trans_dic/P16A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 15,46</t>
+          <t>10,4; 15,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,47</t>
+          <t>14,35; 20,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,16</t>
+          <t>16,06; 21,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 31,02</t>
+          <t>23,77; 31,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,0</t>
+          <t>17,37; 23,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,65; 36,97</t>
+          <t>29,86; 36,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,08; 36,4</t>
+          <t>29,15; 36,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,35; 42,9</t>
+          <t>36,94; 42,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,5</t>
+          <t>14,63; 18,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,01; 27,77</t>
+          <t>22,76; 27,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,52; 28,34</t>
+          <t>23,59; 28,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,85; 36,67</t>
+          <t>31,58; 36,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 15,62</t>
+          <t>11,29; 15,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 21,7</t>
+          <t>16,6; 21,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 22,63</t>
+          <t>17,2; 22,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 22,98</t>
+          <t>8,29; 22,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 24,58</t>
+          <t>19,38; 24,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 34,75</t>
+          <t>28,72; 34,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,78; 31,62</t>
+          <t>25,82; 31,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,7; 41,93</t>
+          <t>36,86; 42,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 19,4</t>
+          <t>16,01; 19,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,31; 27,41</t>
+          <t>23,5; 27,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 26,18</t>
+          <t>22,1; 26,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,29; 31,25</t>
+          <t>18,32; 31,23</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,3</t>
+          <t>10,06; 15,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,53</t>
+          <t>13,74; 19,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,44</t>
+          <t>12,37; 17,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,64; 26,65</t>
+          <t>19,53; 26,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,63; 29,59</t>
+          <t>22,79; 29,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,26; 35,46</t>
+          <t>28,41; 35,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,21; 31,81</t>
+          <t>25,13; 31,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,72; 72,98</t>
+          <t>34,62; 75,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 21,23</t>
+          <t>17,06; 21,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 26,42</t>
+          <t>22,18; 26,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,74; 23,94</t>
+          <t>19,52; 23,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,78; 59,33</t>
+          <t>28,8; 58,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 19,03</t>
+          <t>14,06; 18,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 20,75</t>
+          <t>15,64; 20,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 23,72</t>
+          <t>18,33; 23,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,33; 28,35</t>
+          <t>22,41; 28,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,09; 29,71</t>
+          <t>23,92; 29,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,72; 39,85</t>
+          <t>33,73; 39,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,96; 38,0</t>
+          <t>31,5; 37,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 41,95</t>
+          <t>31,19; 42,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,06; 23,6</t>
+          <t>20,14; 23,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 30,13</t>
+          <t>25,89; 30,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,14; 30,31</t>
+          <t>26,18; 30,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,65</t>
+          <t>28,6; 34,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 15,25</t>
+          <t>12,82; 15,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,55; 19,24</t>
+          <t>16,51; 19,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,67; 20,21</t>
+          <t>17,57; 20,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,4; 24,74</t>
+          <t>17,53; 24,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,42</t>
+          <t>22,43; 25,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 35,15</t>
+          <t>31,96; 35,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,45; 32,61</t>
+          <t>29,51; 32,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,91; 53,16</t>
+          <t>37,63; 51,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 19,95</t>
+          <t>17,99; 19,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,79; 26,98</t>
+          <t>24,81; 27,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,02; 26,25</t>
+          <t>24,12; 26,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,14; 39,03</t>
+          <t>29,35; 38,79</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72969; 107125</t>
+          <t>72071; 106653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103711; 143465</t>
+          <t>100544; 142344</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109342; 149541</t>
+          <t>108357; 147076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149312; 197127</t>
+          <t>151015; 198564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>119523; 158317</t>
+          <t>119574; 158439</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>206355; 257344</t>
+          <t>207837; 257458</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>195638; 244882</t>
+          <t>196163; 245648</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>252380; 289921</t>
+          <t>249625; 289549</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>201796; 255593</t>
+          <t>202065; 254656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>321396; 387895</t>
+          <t>317908; 383367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>316909; 381918</t>
+          <t>317938; 382338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>417579; 480832</t>
+          <t>414140; 477707</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>106099; 150230</t>
+          <t>108616; 150567</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>167997; 220846</t>
+          <t>168998; 222326</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176894; 231388</t>
+          <t>175860; 229884</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112368; 274155</t>
+          <t>98848; 269880</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>186327; 238031</t>
+          <t>187644; 238122</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>296273; 357587</t>
+          <t>295545; 356463</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>268869; 329748</t>
+          <t>269249; 330027</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>351599; 401713</t>
+          <t>353143; 402895</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>308358; 374385</t>
+          <t>309063; 377359</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>477040; 561102</t>
+          <t>480984; 558325</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>457316; 540675</t>
+          <t>456423; 540047</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>393374; 672074</t>
+          <t>394075; 671747</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68165; 103809</t>
+          <t>68279; 101893</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103579; 147746</t>
+          <t>103961; 146128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92493; 132463</t>
+          <t>93937; 133224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138391; 187824</t>
+          <t>137649; 190149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>154732; 202347</t>
+          <t>155850; 203448</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>219407; 275248</t>
+          <t>220543; 275919</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>197883; 249685</t>
+          <t>197266; 249905</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>324103; 681141</t>
+          <t>323119; 700785</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>231658; 289182</t>
+          <t>232458; 288916</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>336332; 404928</t>
+          <t>339935; 407976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>304964; 369734</t>
+          <t>301566; 369353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>471410; 971931</t>
+          <t>471685; 958835</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>136809; 179303</t>
+          <t>132523; 174944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148910; 196320</t>
+          <t>147926; 196355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172285; 222366</t>
+          <t>171815; 220659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207007; 262776</t>
+          <t>207715; 264792</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>250231; 308547</t>
+          <t>248449; 304407</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>354010; 418361</t>
+          <t>354101; 419510</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>333548; 396643</t>
+          <t>328822; 395406</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>323921; 457851</t>
+          <t>340369; 458847</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>397427; 467391</t>
+          <t>398851; 468008</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>517194; 601306</t>
+          <t>516632; 601453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517976; 600520</t>
+          <t>518635; 600673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>576072; 699230</t>
+          <t>577258; 695684</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>419332; 499643</t>
+          <t>419788; 494030</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>566113; 658389</t>
+          <t>564915; 663418</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>599790; 685922</t>
+          <t>596489; 685443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>602104; 855818</t>
+          <t>606557; 862316</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>760960; 859025</t>
+          <t>758119; 857376</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1129279; 1248204</t>
+          <t>1134909; 1247662</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1043727; 1156043</t>
+          <t>1045830; 1162104</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1387080; 1944977</t>
+          <t>1376601; 1886597</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1199751; 1327515</t>
+          <t>1197256; 1327501</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1728497; 1880953</t>
+          <t>1729485; 1884212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1666980; 1821371</t>
+          <t>1673737; 1828832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2074461; 2778298</t>
+          <t>2089193; 2761143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A02-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 15,39</t>
+          <t>10,41; 15,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 20,31</t>
+          <t>14,62; 20,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,06; 21,8</t>
+          <t>16,18; 22,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,77; 31,25</t>
+          <t>23,74; 31,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,02</t>
+          <t>17,5; 23,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,86; 36,99</t>
+          <t>29,51; 36,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15; 36,51</t>
+          <t>29,21; 36,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,94; 42,85</t>
+          <t>36,7; 42,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 18,44</t>
+          <t>14,61; 18,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,45</t>
+          <t>22,97; 27,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,59; 28,37</t>
+          <t>23,48; 28,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,58; 36,43</t>
+          <t>31,48; 36,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,65</t>
+          <t>11,18; 15,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 21,84</t>
+          <t>16,78; 21,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 22,48</t>
+          <t>17,05; 22,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 22,62</t>
+          <t>18,6; 24,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 24,59</t>
+          <t>19,38; 25,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,72; 34,64</t>
+          <t>28,58; 34,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,82; 31,64</t>
+          <t>25,73; 31,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,86; 42,05</t>
+          <t>36,25; 41,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 19,55</t>
+          <t>16,02; 19,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 27,28</t>
+          <t>23,54; 27,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,1; 26,15</t>
+          <t>22,19; 26,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,32; 31,23</t>
+          <t>28,47; 32,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 15,02</t>
+          <t>9,86; 14,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,32</t>
+          <t>13,71; 19,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,37; 17,54</t>
+          <t>12,51; 17,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,53; 26,98</t>
+          <t>19,41; 25,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,79; 29,75</t>
+          <t>22,62; 29,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,41; 35,54</t>
+          <t>28,43; 35,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,13; 31,83</t>
+          <t>25,3; 31,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,62; 75,08</t>
+          <t>33,41; 39,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,06; 21,21</t>
+          <t>17,13; 21,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,18; 26,62</t>
+          <t>22,03; 26,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,52; 23,91</t>
+          <t>19,34; 23,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,8; 58,54</t>
+          <t>27,35; 31,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 18,57</t>
+          <t>14,43; 18,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 20,76</t>
+          <t>15,58; 21,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,33; 23,54</t>
+          <t>18,54; 23,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,41; 28,57</t>
+          <t>22,14; 27,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,92; 29,31</t>
+          <t>23,88; 29,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,73; 39,96</t>
+          <t>33,65; 39,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 37,88</t>
+          <t>31,6; 37,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,19; 42,04</t>
+          <t>37,73; 42,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 23,63</t>
+          <t>20,08; 23,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 30,14</t>
+          <t>25,96; 30,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,18; 30,32</t>
+          <t>26,11; 30,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,6; 34,47</t>
+          <t>30,93; 34,88</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 15,08</t>
+          <t>12,79; 15,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,51; 19,39</t>
+          <t>16,42; 19,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 20,19</t>
+          <t>17,53; 20,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 24,92</t>
+          <t>22,26; 25,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,37</t>
+          <t>22,27; 25,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,96; 35,14</t>
+          <t>31,8; 35,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,51; 32,79</t>
+          <t>29,64; 32,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,63; 51,57</t>
+          <t>37,54; 40,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,95</t>
+          <t>17,95; 19,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,81; 27,02</t>
+          <t>24,74; 26,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,12; 26,36</t>
+          <t>24,12; 26,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,35; 38,79</t>
+          <t>30,63; 32,62</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>173659</t>
+          <t>190046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>270921</t>
+          <t>290148</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>444581</t>
+          <t>480194</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72071; 106653</t>
+          <t>72171; 108224</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100544; 142344</t>
+          <t>102457; 142508</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108357; 147076</t>
+          <t>109186; 150804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>151015; 198564</t>
+          <t>163985; 215009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>119574; 158439</t>
+          <t>120441; 161039</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>207837; 257458</t>
+          <t>205368; 256563</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>196163; 245648</t>
+          <t>196561; 247095</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249625; 289549</t>
+          <t>269079; 311613</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>202065; 254656</t>
+          <t>201857; 255783</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>317908; 383367</t>
+          <t>320844; 388210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>317938; 382338</t>
+          <t>316447; 381722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>414140; 477707</t>
+          <t>448249; 517786</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207499</t>
+          <t>224970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>376901</t>
+          <t>417875</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>584400</t>
+          <t>642845</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>108616; 150567</t>
+          <t>107505; 150989</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>168998; 222326</t>
+          <t>170861; 223226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175860; 229884</t>
+          <t>174370; 226883</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98848; 269880</t>
+          <t>195134; 253561</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>187644; 238122</t>
+          <t>187672; 244604</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>295545; 356463</t>
+          <t>294032; 357135</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>269249; 330027</t>
+          <t>268306; 329072</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>353143; 402895</t>
+          <t>388139; 444246</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>309063; 377359</t>
+          <t>309293; 375926</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>480984; 558325</t>
+          <t>481836; 556651</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>456423; 540047</t>
+          <t>458307; 541408</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>394075; 671747</t>
+          <t>603459; 685281</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162113</t>
+          <t>180676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>467984</t>
+          <t>297675</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>630097</t>
+          <t>478352</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68279; 101893</t>
+          <t>66905; 101385</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103961; 146128</t>
+          <t>103688; 146174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93937; 133224</t>
+          <t>95025; 133164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137649; 190149</t>
+          <t>155844; 208413</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>155850; 203448</t>
+          <t>154697; 200383</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>220543; 275919</t>
+          <t>220691; 273770</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>197266; 249905</t>
+          <t>198638; 247096</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>323119; 700785</t>
+          <t>271348; 321373</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>232458; 288916</t>
+          <t>233364; 292131</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>339935; 407976</t>
+          <t>337754; 409165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>301566; 369353</t>
+          <t>298666; 365841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>471685; 958835</t>
+          <t>441807; 513891</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233522</t>
+          <t>243634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>418576</t>
+          <t>448810</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>652098</t>
+          <t>692444</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132523; 174944</t>
+          <t>135917; 178627</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>147926; 196355</t>
+          <t>147418; 198898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171815; 220659</t>
+          <t>173790; 224173</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207715; 264792</t>
+          <t>219212; 271951</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>248449; 304407</t>
+          <t>248020; 306453</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>354101; 419510</t>
+          <t>353236; 417649</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>328822; 395406</t>
+          <t>329879; 392817</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>340369; 458847</t>
+          <t>421421; 477048</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>398851; 468008</t>
+          <t>397790; 470788</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>516632; 601453</t>
+          <t>518052; 601011</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>518635; 600673</t>
+          <t>517297; 601267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>577258; 695684</t>
+          <t>651809; 734875</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>776794</t>
+          <t>839327</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1534383</t>
+          <t>1454508</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2311177</t>
+          <t>2293836</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>419788; 494030</t>
+          <t>418796; 496828</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>564915; 663418</t>
+          <t>561679; 661042</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>596489; 685443</t>
+          <t>595150; 688038</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>606557; 862316</t>
+          <t>786469; 898424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>758119; 857376</t>
+          <t>752583; 853098</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1134909; 1247662</t>
+          <t>1129220; 1246793</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1045830; 1162104</t>
+          <t>1050441; 1161428</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1376601; 1886597</t>
+          <t>1401329; 1502432</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1197256; 1327501</t>
+          <t>1194525; 1326086</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1729485; 1884212</t>
+          <t>1725197; 1880104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1673737; 1828832</t>
+          <t>1673551; 1815264</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2089193; 2761143</t>
+          <t>2225276; 2370307</t>
         </is>
       </c>
     </row>
